--- a/detections_log.xlsx
+++ b/detections_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -665,6 +665,456 @@
       </c>
       <c r="K5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-03-02T10:33:31_2425526000</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-03-02T10:33:31</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2.426 GHz</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2.42553</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-111.06</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Bluetooth (2.4 GHz)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2.41 GHz</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="I6" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-03-02T10:33:31_2426458000</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-03-02T10:33:31</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2.426 GHz</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2.42646</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-111.06</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bluetooth (2.4 GHz)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2.41 GHz</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="I7" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-03-02T10:33:33_2466826800</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-03-02T10:33:33</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2.467 GHz</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2.46683</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-116.71</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bluetooth (2.4 GHz)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2.45 GHz</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="I8" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-03-02T10:33:33_2467161200</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-03-02T10:33:33</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2.467 GHz</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2.46716</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-116.71</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bluetooth (2.4 GHz)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2.45 GHz</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="I9" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-03-02T10:33:35_2480133600</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-03-02T10:33:35</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2.48 GHz</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2.48013</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-121.78</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bluetooth (2.4 GHz)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2.49 GHz</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="I10" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-03-02T10:33:31_2425526000</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-03-02T10:33:31</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2.426 GHz</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2.42553</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-111.06</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bluetooth (2.4 GHz)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2.41 GHz</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="I11" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-03-02T10:33:31_2426458000</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-03-02T10:33:31</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2.426 GHz</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2.42646</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-111.06</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bluetooth (2.4 GHz)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2.41 GHz</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="I12" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-03-02T10:33:33_2466826800</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-03-02T10:33:33</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2.467 GHz</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2.46683</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-116.71</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Bluetooth (2.4 GHz)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2.45 GHz</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="I13" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-03-02T10:33:33_2467161200</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-03-02T10:33:33</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2.467 GHz</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2.46716</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-116.71</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Bluetooth (2.4 GHz)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2.45 GHz</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="I14" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-03-02T10:33:35_2480133600</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-03-02T10:33:35</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2.48 GHz</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2.48013</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-121.78</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Bluetooth (2.4 GHz)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2.49 GHz</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="I15" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
